--- a/leave_of_absence_forms/030_creative_leave_of_absence_request--leave_of_absence_forms.xlsx
+++ b/leave_of_absence_forms/030_creative_leave_of_absence_request--leave_of_absence_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'sick'}</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Sick'}</t>
+          <t>Sick</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'emergency'}</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency'}</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'parental'}</t>
+          <t>parental</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Parental'}</t>
+          <t>Parental</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'no_response'}</t>
+          <t>no_response</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'No Response'}</t>
+          <t>No Response</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'acknowledged'}</t>
+          <t>acknowledged</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Acknowledged'}</t>
+          <t>Acknowledged</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_acknowledged'}</t>
+          <t>not_acknowledged</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Not Acknowledged'}</t>
+          <t>Not Acknowledged</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'no_response'}</t>
+          <t>no_response</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'No Response'}</t>
+          <t>No Response</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'acknowledged'}</t>
+          <t>acknowledged</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Acknowledged'}</t>
+          <t>Acknowledged</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_acknowledged'}</t>
+          <t>not_acknowledged</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not Acknowledged'}</t>
+          <t>Not Acknowledged</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'no_response'}</t>
+          <t>no_response</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'No Response'}</t>
+          <t>No Response</t>
         </is>
       </c>
     </row>
